--- a/25-26/AA Stone Trading- B K Exports SOA.xlsx
+++ b/25-26/AA Stone Trading- B K Exports SOA.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
   <si>
     <t>invoice number</t>
   </si>
@@ -125,9 +125,6 @@
     <t>payment date</t>
   </si>
   <si>
-    <t>total</t>
-  </si>
-  <si>
     <t>payment made by AA Stone</t>
   </si>
   <si>
@@ -144,13 +141,34 @@
   </si>
   <si>
     <t>pending</t>
+  </si>
+  <si>
+    <t>BK035</t>
+  </si>
+  <si>
+    <t>BK036</t>
+  </si>
+  <si>
+    <t>BK038</t>
+  </si>
+  <si>
+    <t>BK039</t>
+  </si>
+  <si>
+    <t>BK040</t>
+  </si>
+  <si>
+    <t>BK041</t>
+  </si>
+  <si>
+    <t>BK043</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,16 +183,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,12 +206,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -288,8 +292,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -297,9 +299,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -312,27 +311,36 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -397,10 +405,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -418,100 +432,72 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -826,15 +812,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="14"/>
+    <col min="6" max="6" width="9.140625" style="11"/>
     <col min="7" max="7" width="23.7109375" customWidth="1"/>
     <col min="13" max="13" width="28.7109375" customWidth="1"/>
     <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -847,16 +833,16 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="11" t="s">
         <v>3</v>
       </c>
       <c r="G1" t="s">
@@ -864,49 +850,49 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="3">
         <v>7919.25</v>
       </c>
-      <c r="C2" s="67">
+      <c r="C2" s="54">
         <v>17843</v>
       </c>
-      <c r="D2" s="77">
+      <c r="D2" s="47">
         <v>17843</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="64">
         <v>45810</v>
       </c>
-      <c r="F2" s="45">
+      <c r="F2" s="49">
         <f>C2-D2</f>
         <v>0</v>
       </c>
       <c r="K2" s="40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L2" s="40"/>
       <c r="M2" s="40"/>
       <c r="N2" s="40"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="3">
         <v>9923.2900000000009</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="46"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="66"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>32</v>
@@ -919,17 +905,17 @@
       <c r="B4" s="3">
         <v>9118.02</v>
       </c>
-      <c r="C4" s="69">
+      <c r="C4" s="15">
         <f>B4</f>
         <v>9118.02</v>
       </c>
-      <c r="D4" s="79">
+      <c r="D4" s="16">
         <v>9118.02</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="7">
         <v>45814</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="12">
         <f>C4-D4</f>
         <v>0</v>
       </c>
@@ -953,16 +939,16 @@
       <c r="B5" s="3">
         <v>10472.85</v>
       </c>
-      <c r="C5" s="56">
+      <c r="C5" s="57">
         <v>19109.25</v>
       </c>
-      <c r="D5" s="80">
+      <c r="D5" s="58">
         <v>19109.25</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="51">
         <v>45827</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="59">
         <f>C5-D5</f>
         <v>0</v>
       </c>
@@ -980,20 +966,20 @@
       <c r="B6" s="3">
         <v>8636.4</v>
       </c>
-      <c r="C6" s="56"/>
-      <c r="D6" s="80"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="58"/>
       <c r="E6" s="61"/>
-      <c r="F6" s="57"/>
+      <c r="F6" s="60"/>
       <c r="K6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="10">
         <v>9118</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="10">
         <v>9118</v>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="9">
         <v>45814</v>
       </c>
     </row>
@@ -1004,14 +990,14 @@
       <c r="B7" s="3">
         <v>9999.76</v>
       </c>
-      <c r="C7" s="70">
+      <c r="C7" s="54">
         <f>B7+B8+B9</f>
         <v>25190.3</v>
       </c>
-      <c r="D7" s="81">
+      <c r="D7" s="47">
         <v>5632.5</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="51">
         <v>45866</v>
       </c>
       <c r="F7" s="42">
@@ -1024,7 +1010,7 @@
       <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="83">
+      <c r="L7" s="62">
         <v>19109</v>
       </c>
       <c r="M7" s="37">
@@ -1041,15 +1027,15 @@
       <c r="B8" s="3">
         <v>8615.16</v>
       </c>
-      <c r="C8" s="71"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="50"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="52"/>
       <c r="F8" s="43"/>
       <c r="G8" s="32"/>
       <c r="K8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="83"/>
+      <c r="L8" s="62"/>
       <c r="M8" s="37"/>
       <c r="N8" s="36"/>
     </row>
@@ -1060,11 +1046,11 @@
       <c r="B9" s="3">
         <v>6575.38</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="79">
+      <c r="C9" s="56"/>
+      <c r="D9" s="16">
         <v>20601.46</v>
       </c>
-      <c r="E9" s="51"/>
+      <c r="E9" s="53"/>
       <c r="F9" s="44"/>
       <c r="G9" s="32"/>
       <c r="K9" s="1" t="s">
@@ -1073,7 +1059,7 @@
       <c r="L9" s="37">
         <v>25190</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="10">
         <v>5632</v>
       </c>
       <c r="N9" s="36">
@@ -1081,23 +1067,23 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="3">
         <v>7827.3</v>
       </c>
-      <c r="C10" s="73">
+      <c r="C10" s="45">
         <f>B10+B11</f>
         <v>17788.939999999999</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="63">
         <v>16954.599999999999</v>
       </c>
-      <c r="E10" s="54">
+      <c r="E10" s="51">
         <v>45870</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="49">
         <f>C10-D10</f>
         <v>834.34000000000015</v>
       </c>
@@ -1114,16 +1100,16 @@
       <c r="N10" s="37"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="3">
         <v>9961.64</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="53"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="50"/>
       <c r="G11" s="32"/>
       <c r="K11" s="1" t="s">
         <v>11</v>
@@ -1139,31 +1125,31 @@
       <c r="B12" s="3">
         <v>10487.4</v>
       </c>
-      <c r="C12" s="75">
+      <c r="C12" s="45">
         <f>B12+B13</f>
         <v>20081.010000000002</v>
       </c>
-      <c r="D12" s="81">
+      <c r="D12" s="47">
         <v>19870</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="51">
         <v>45874</v>
       </c>
-      <c r="F12" s="47">
+      <c r="F12" s="49">
         <f>C12-D12</f>
         <v>211.01000000000204</v>
       </c>
       <c r="G12" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="8"/>
+      <c r="I12" s="6"/>
       <c r="K12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="L12" s="37">
         <v>17789</v>
       </c>
-      <c r="M12" s="83">
+      <c r="M12" s="62">
         <v>16954</v>
       </c>
       <c r="N12" s="36">
@@ -1177,16 +1163,16 @@
       <c r="B13" s="3">
         <v>9593.61</v>
       </c>
-      <c r="C13" s="76"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="48"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="50"/>
       <c r="G13" s="32"/>
       <c r="K13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="L13" s="37"/>
-      <c r="M13" s="83"/>
+      <c r="M13" s="62"/>
       <c r="N13" s="37"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1196,17 +1182,17 @@
       <c r="B14" s="3">
         <v>10343.030000000001</v>
       </c>
-      <c r="C14" s="75">
+      <c r="C14" s="45">
         <f>B14+B15</f>
         <v>21994.18</v>
       </c>
-      <c r="D14" s="81">
+      <c r="D14" s="47">
         <v>22506.639999999999</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="51">
         <v>45897</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="49">
         <f>C14-D14</f>
         <v>-512.45999999999913</v>
       </c>
@@ -1233,10 +1219,10 @@
       <c r="B15" s="3">
         <v>11651.15</v>
       </c>
-      <c r="C15" s="76"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="48"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="50"/>
       <c r="G15" s="32"/>
       <c r="K15" s="1" t="s">
         <v>15</v>
@@ -1252,317 +1238,360 @@
       <c r="B16" s="3">
         <v>9620.1299999999992</v>
       </c>
-      <c r="C16" s="69">
+      <c r="C16" s="15">
         <f>B16</f>
         <v>9620.1299999999992</v>
       </c>
-      <c r="D16" s="79">
+      <c r="D16" s="16">
         <v>10448.1</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="7">
         <v>45930</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="12">
         <f>C16-D16</f>
         <v>-827.97000000000116</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="14" t="s">
         <v>30</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="37">
+      <c r="L16" s="19">
         <v>21994</v>
       </c>
-      <c r="M16" s="37">
+      <c r="M16" s="19">
         <v>22506</v>
       </c>
-      <c r="N16" s="36">
+      <c r="N16" s="20">
         <v>45897</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="62"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="64">
-        <f>SUM(C2:C16)</f>
-        <v>140744.83000000002</v>
-      </c>
-      <c r="D17" s="65">
-        <f>SUM(D2:D16)</f>
-        <v>142083.57000000004</v>
-      </c>
-      <c r="E17" s="66"/>
-      <c r="F17" s="64">
-        <f>SUM(F2:F16)</f>
-        <v>-1338.739999999998</v>
-      </c>
-      <c r="G17" s="18"/>
-      <c r="K17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" s="37"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
+      <c r="A17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="4">
+        <v>8801.9</v>
+      </c>
+      <c r="C17" s="34">
+        <f>B17+B18</f>
+        <v>18510.77</v>
+      </c>
+      <c r="D17" s="35">
+        <v>15018</v>
+      </c>
+      <c r="E17" s="36">
+        <v>45946</v>
+      </c>
+      <c r="F17" s="34">
+        <f>C17-D17</f>
+        <v>3492.7700000000004</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="62"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="18"/>
-      <c r="K18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L18" s="13">
-        <v>9620</v>
-      </c>
-      <c r="M18" s="13">
-        <v>10448</v>
-      </c>
-      <c r="N18" s="12">
-        <v>45930</v>
+      <c r="A18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="4">
+        <v>9708.8700000000008</v>
+      </c>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="33"/>
+      <c r="M18" t="s">
+        <v>36</v>
+      </c>
+      <c r="N18">
+        <v>3492</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="18"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="19"/>
+      <c r="A19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="4">
+        <v>9192.35</v>
+      </c>
+      <c r="C19" s="34">
+        <f>B19+B20+B21+B22</f>
+        <v>32852.65</v>
+      </c>
+      <c r="D19" s="38">
+        <v>20179.62</v>
+      </c>
+      <c r="E19" s="39">
+        <v>45959</v>
+      </c>
+      <c r="F19" s="24">
+        <f>C19-D19-D21</f>
+        <v>3503.0300000000025</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="18"/>
-      <c r="K20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L20" s="1">
-        <f>SUM(L4:L18)</f>
-        <v>140744</v>
-      </c>
-      <c r="M20" s="1">
-        <f>SUM(M4:M18)</f>
-        <v>142081</v>
-      </c>
-      <c r="N20" s="84">
-        <f>M20-L20</f>
-        <v>1337</v>
+      <c r="A20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="4">
+        <v>5823.61</v>
+      </c>
+      <c r="C20" s="35"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="33"/>
+      <c r="M20" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="N20" s="17" t="e">
+        <f>N18-N19</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B21" s="4">
-        <v>8801.9</v>
-      </c>
-      <c r="C21" s="34">
-        <f>B21+B22</f>
-        <v>18510.77</v>
-      </c>
-      <c r="D21" s="35">
-        <v>15018</v>
-      </c>
-      <c r="E21" s="36">
-        <v>45946</v>
-      </c>
-      <c r="F21" s="34">
-        <f>C21-D21</f>
-        <v>3492.7700000000004</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>31</v>
-      </c>
+        <v>8138.34</v>
+      </c>
+      <c r="C21" s="35"/>
+      <c r="D21" s="11">
+        <v>9170</v>
+      </c>
+      <c r="E21" s="8">
+        <v>45960</v>
+      </c>
+      <c r="F21" s="41"/>
+      <c r="G21" s="33"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B22" s="4">
-        <v>9708.8700000000008</v>
+        <v>9698.35</v>
       </c>
       <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="35"/>
+      <c r="F22" s="25"/>
       <c r="G22" s="33"/>
-      <c r="M22" t="s">
-        <v>37</v>
-      </c>
-      <c r="N22">
-        <v>3492</v>
-      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B23" s="4">
-        <v>9192.35</v>
-      </c>
-      <c r="C23" s="34">
-        <f>B23+B24+B25+B26</f>
-        <v>32852.65</v>
-      </c>
-      <c r="D23" s="38">
-        <v>20179.62</v>
-      </c>
-      <c r="E23" s="39">
-        <v>45959</v>
-      </c>
-      <c r="F23" s="24">
-        <f>C23-D23-D25</f>
-        <v>3503.0300000000025</v>
+        <v>8123.74</v>
+      </c>
+      <c r="C23" s="24">
+        <f>B23+B24</f>
+        <v>18721.400000000001</v>
+      </c>
+      <c r="D23" s="26">
+        <v>22291.21</v>
+      </c>
+      <c r="E23" s="28">
+        <v>45981</v>
+      </c>
+      <c r="F23" s="30">
+        <f>C23-D23</f>
+        <v>-3569.8099999999977</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="M23" t="s">
-        <v>38</v>
-      </c>
-      <c r="N23">
-        <v>1337</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B24" s="4">
-        <v>5823.61</v>
-      </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="41"/>
+        <v>10597.66</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="31"/>
       <c r="G24" s="33"/>
-      <c r="M24" s="85" t="s">
-        <v>39</v>
-      </c>
-      <c r="N24" s="85">
-        <f>N22-N23</f>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="23"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B26" s="4"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="23"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74">
         <v>2155</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="4">
-        <v>8138.34</v>
-      </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="14">
-        <v>9170</v>
-      </c>
-      <c r="E25" s="10">
-        <v>45960</v>
-      </c>
-      <c r="F25" s="41"/>
-      <c r="G25" s="33"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="4">
-        <v>9698.35</v>
-      </c>
-      <c r="C26" s="35"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="33"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="4">
-        <v>8123.74</v>
-      </c>
-      <c r="C27" s="24">
-        <f>B27+B28</f>
-        <v>18721.400000000001</v>
-      </c>
-      <c r="D27" s="26">
-        <v>22291.21</v>
-      </c>
-      <c r="E27" s="28">
-        <v>45981</v>
-      </c>
-      <c r="F27" s="30">
-        <f>C27-D27</f>
-        <v>-3569.8099999999977</v>
-      </c>
-      <c r="G27" s="33" t="s">
-        <v>30</v>
-      </c>
+      <c r="G27" s="23"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B28" s="4">
-        <v>10597.66</v>
-      </c>
-      <c r="C28" s="25"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="33"/>
+        <v>8084.34</v>
+      </c>
+      <c r="C28" s="67">
+        <f>B28+B29</f>
+        <v>17122.580000000002</v>
+      </c>
+      <c r="D28" s="69">
+        <v>20031</v>
+      </c>
+      <c r="E28" s="71">
+        <v>46029</v>
+      </c>
+      <c r="F28" s="67">
+        <f>C28-D28</f>
+        <v>-2908.4199999999983</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C29" s="17">
-        <f>SUM(C2:C28)</f>
-        <v>351574.4800000001</v>
-      </c>
-      <c r="D29" s="14">
-        <f>SUM(D2:D28)</f>
-        <v>350825.97000000009</v>
-      </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="17">
-        <f>SUM(F2:F28)</f>
-        <v>748.51000000000931</v>
-      </c>
-      <c r="G29" s="18" t="s">
+      <c r="A29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="4">
+        <v>9038.24</v>
+      </c>
+      <c r="C29" s="68"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="32"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="4">
+        <v>9877.56</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="21"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="4">
+        <v>8311.7099999999991</v>
+      </c>
+      <c r="C31" s="67">
+        <f>B31+B32</f>
+        <v>16174.68</v>
+      </c>
+      <c r="D31" s="69">
+        <v>15028</v>
+      </c>
+      <c r="E31" s="18"/>
+      <c r="F31" s="67">
+        <f>C31-D31</f>
+        <v>1146.6800000000003</v>
+      </c>
+      <c r="G31" s="75" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="22"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="21"/>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="4">
+        <v>7862.97</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="75"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="4">
+        <v>10574.88</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="21"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="4">
+        <v>9825.43</v>
+      </c>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="21"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C36" s="13">
+        <f>SUM(C28:C35)</f>
+        <v>33297.26</v>
+      </c>
+      <c r="D36" s="13">
+        <f>SUM(D28:D35)</f>
+        <v>35059</v>
+      </c>
+      <c r="F36" s="13">
+        <f>SUM(F27:F35)</f>
+        <v>393.26000000000204</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="62">
+  <mergeCells count="68">
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
     <mergeCell ref="K2:N2"/>
-    <mergeCell ref="L16:L17"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="M7:M8"/>
@@ -1571,8 +1600,6 @@
     <mergeCell ref="N9:N11"/>
     <mergeCell ref="M14:M15"/>
     <mergeCell ref="N14:N15"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="N16:N17"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="N12:N13"/>
     <mergeCell ref="L4:L5"/>
@@ -1591,9 +1618,9 @@
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F22"/>
     <mergeCell ref="F7:F9"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="C12:C13"/>
@@ -1607,22 +1634,22 @@
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
     <mergeCell ref="G7:G9"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G26"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="C19:C22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/25-26/AA Stone Trading- B K Exports SOA.xlsx
+++ b/25-26/AA Stone Trading- B K Exports SOA.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
   <si>
     <t>invoice number</t>
   </si>
@@ -137,12 +137,6 @@
     <t>you deducted</t>
   </si>
   <si>
-    <t>actual deduction</t>
-  </si>
-  <si>
-    <t>pending</t>
-  </si>
-  <si>
     <t>BK035</t>
   </si>
   <si>
@@ -162,6 +156,15 @@
   </si>
   <si>
     <t>BK043</t>
+  </si>
+  <si>
+    <t>BK046</t>
+  </si>
+  <si>
+    <t>dedcut</t>
+  </si>
+  <si>
+    <t>clear</t>
   </si>
 </sst>
 </file>
@@ -283,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -320,184 +323,168 @@
     <xf numFmtId="4" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,13 +799,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="63" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="11"/>
     <col min="7" max="7" width="23.7109375" customWidth="1"/>
@@ -836,7 +823,7 @@
       <c r="C1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="63" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -856,25 +843,25 @@
       <c r="B2" s="3">
         <v>7919.25</v>
       </c>
-      <c r="C2" s="54">
+      <c r="C2" s="35">
         <v>17843</v>
       </c>
-      <c r="D2" s="47">
+      <c r="D2" s="67">
         <v>17843</v>
       </c>
-      <c r="E2" s="64">
+      <c r="E2" s="40">
         <v>45810</v>
       </c>
-      <c r="F2" s="49">
+      <c r="F2" s="32">
         <f>C2-D2</f>
         <v>0</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -883,10 +870,10 @@
       <c r="B3" s="3">
         <v>9923.2900000000009</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="66"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="34"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
         <v>35</v>
@@ -909,7 +896,7 @@
         <f>B4</f>
         <v>9118.02</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="69">
         <v>9118.02</v>
       </c>
       <c r="E4" s="7">
@@ -922,13 +909,13 @@
       <c r="K4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="37">
+      <c r="L4" s="28">
         <v>17843</v>
       </c>
-      <c r="M4" s="40">
+      <c r="M4" s="26">
         <v>17843</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="27">
         <v>45810</v>
       </c>
     </row>
@@ -939,25 +926,25 @@
       <c r="B5" s="3">
         <v>10472.85</v>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="37">
         <v>19109.25</v>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="70">
         <v>19109.25</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="30">
         <v>45827</v>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="38">
         <f>C5-D5</f>
         <v>0</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="37"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="37"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="28"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -966,10 +953,10 @@
       <c r="B6" s="3">
         <v>8636.4</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="60"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="39"/>
       <c r="K6" s="1" t="s">
         <v>6</v>
       </c>
@@ -990,33 +977,33 @@
       <c r="B7" s="3">
         <v>9999.76</v>
       </c>
-      <c r="C7" s="54">
+      <c r="C7" s="35">
         <f>B7+B8+B9</f>
         <v>25190.3</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="67">
         <v>5632.5</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="30">
         <v>45866</v>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="47">
         <f>C7-D7-D9</f>
         <v>-1043.6599999999999</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="62">
+      <c r="L7" s="29">
         <v>19109</v>
       </c>
-      <c r="M7" s="37">
+      <c r="M7" s="28">
         <v>19109</v>
       </c>
-      <c r="N7" s="36">
+      <c r="N7" s="27">
         <v>45827</v>
       </c>
     </row>
@@ -1027,17 +1014,17 @@
       <c r="B8" s="3">
         <v>8615.16</v>
       </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="48"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="68"/>
       <c r="E8" s="52"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="32"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="23"/>
       <c r="K8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="62"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="36"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="27"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -1046,23 +1033,23 @@
       <c r="B9" s="3">
         <v>6575.38</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="16">
+      <c r="C9" s="36"/>
+      <c r="D9" s="69">
         <v>20601.46</v>
       </c>
-      <c r="E9" s="53"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="32"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="23"/>
       <c r="K9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="37">
+      <c r="L9" s="28">
         <v>25190</v>
       </c>
       <c r="M9" s="10">
         <v>5632</v>
       </c>
-      <c r="N9" s="36">
+      <c r="N9" s="27">
         <v>45866</v>
       </c>
     </row>
@@ -1073,31 +1060,31 @@
       <c r="B10" s="3">
         <v>7827.3</v>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="50">
         <f>B10+B11</f>
         <v>17788.939999999999</v>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="71">
         <v>16954.599999999999</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="30">
         <v>45870</v>
       </c>
-      <c r="F10" s="49">
+      <c r="F10" s="32">
         <f>C10-D10</f>
         <v>834.34000000000015</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="23" t="s">
         <v>31</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37">
+      <c r="L10" s="28"/>
+      <c r="M10" s="28">
         <v>20601</v>
       </c>
-      <c r="N10" s="37"/>
+      <c r="N10" s="28"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
@@ -1106,17 +1093,17 @@
       <c r="B11" s="3">
         <v>9961.64</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="32"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="23"/>
       <c r="K11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L11" s="37"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -1125,34 +1112,34 @@
       <c r="B12" s="3">
         <v>10487.4</v>
       </c>
-      <c r="C12" s="45">
+      <c r="C12" s="50">
         <f>B12+B13</f>
         <v>20081.010000000002</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="67">
         <v>19870</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="30">
         <v>45874</v>
       </c>
-      <c r="F12" s="49">
+      <c r="F12" s="32">
         <f>C12-D12</f>
         <v>211.01000000000204</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="23" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="6"/>
       <c r="K12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L12" s="37">
+      <c r="L12" s="28">
         <v>17789</v>
       </c>
-      <c r="M12" s="62">
+      <c r="M12" s="29">
         <v>16954</v>
       </c>
-      <c r="N12" s="36">
+      <c r="N12" s="27">
         <v>45870</v>
       </c>
     </row>
@@ -1163,17 +1150,17 @@
       <c r="B13" s="3">
         <v>9593.61</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="32"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="23"/>
       <c r="K13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L13" s="37"/>
-      <c r="M13" s="62"/>
-      <c r="N13" s="37"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="28"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1182,33 +1169,33 @@
       <c r="B14" s="3">
         <v>10343.030000000001</v>
       </c>
-      <c r="C14" s="45">
+      <c r="C14" s="50">
         <f>B14+B15</f>
         <v>21994.18</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="67">
         <v>22506.639999999999</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="30">
         <v>45897</v>
       </c>
-      <c r="F14" s="49">
+      <c r="F14" s="32">
         <f>C14-D14</f>
         <v>-512.45999999999913</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="28">
         <v>20081</v>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="28">
         <v>19870</v>
       </c>
-      <c r="N14" s="36">
+      <c r="N14" s="27">
         <v>45874</v>
       </c>
     </row>
@@ -1219,17 +1206,17 @@
       <c r="B15" s="3">
         <v>11651.15</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="32"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="23"/>
       <c r="K15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L15" s="37"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -1242,7 +1229,7 @@
         <f>B16</f>
         <v>9620.1299999999992</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="69">
         <v>10448.1</v>
       </c>
       <c r="E16" s="7">
@@ -1258,53 +1245,53 @@
       <c r="K16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="17">
         <v>21994</v>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="17">
         <v>22506</v>
       </c>
-      <c r="N16" s="20">
+      <c r="N16" s="18">
         <v>45897</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="4">
         <v>8801.9</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="59">
         <f>B17+B18</f>
         <v>18510.77</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="61">
         <v>15018</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="27">
         <v>45946</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="59">
         <f>C17-D17</f>
         <v>3492.7700000000004</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="58" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="4">
         <v>9708.8700000000008</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="33"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="58"/>
       <c r="M18" t="s">
         <v>36</v>
       </c>
@@ -1312,312 +1299,351 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="4">
         <v>9192.35</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="59">
         <f>B19+B20+B21+B22</f>
         <v>32852.65</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="73">
         <v>20179.62</v>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="43">
         <v>45959</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="44">
         <f>C19-D19-D21</f>
         <v>3503.0300000000025</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="M19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N19" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="4">
         <v>5823.61</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="33"/>
-      <c r="M20" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="N20" s="17" t="e">
-        <f>N18-N19</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C20" s="60"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="58"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="4">
         <v>8138.34</v>
       </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="11">
+      <c r="C21" s="60"/>
+      <c r="D21" s="63">
         <v>9170</v>
       </c>
       <c r="E21" s="8">
         <v>45960</v>
       </c>
-      <c r="F21" s="41"/>
-      <c r="G21" s="33"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F21" s="45"/>
+      <c r="G21" s="58"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="4">
         <v>9698.35</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="33"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C22" s="60"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="58"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="4">
         <v>8123.74</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="44">
         <f>B23+B24</f>
         <v>18721.400000000001</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="74">
         <v>22291.21</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="54">
         <v>45981</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="56">
         <f>C23-D23</f>
         <v>-3569.8099999999977</v>
       </c>
-      <c r="G23" s="33" t="s">
+      <c r="G23" s="58" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="4">
         <v>10597.66</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="33"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="4"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="23"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="4"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="58"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="4">
+        <v>8084.34</v>
+      </c>
+      <c r="C25" s="64">
+        <f>B25+B26</f>
+        <v>17122.580000000002</v>
+      </c>
+      <c r="D25" s="76">
+        <v>20031.18</v>
+      </c>
+      <c r="E25" s="24">
+        <v>46029</v>
+      </c>
+      <c r="F25" s="19">
+        <f>C25-D25</f>
+        <v>-2908.5999999999985</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="4">
+        <v>9038.24</v>
+      </c>
+      <c r="C26" s="65"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="23"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="4"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74">
-        <v>2155</v>
-      </c>
-      <c r="G27" s="23"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="4">
+        <v>8311.7099999999991</v>
+      </c>
+      <c r="C27" s="64">
+        <f>B27+B28</f>
+        <v>16174.68</v>
+      </c>
+      <c r="D27" s="76">
+        <v>15028</v>
+      </c>
+      <c r="E27" s="25">
+        <v>46039</v>
+      </c>
+      <c r="F27" s="19">
+        <f>C27-D27</f>
+        <v>1146.6800000000003</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="4">
+        <v>7862.97</v>
+      </c>
+      <c r="C28" s="66"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21"/>
+      <c r="L28">
         <v>39</v>
       </c>
-      <c r="B28" s="4">
-        <v>8084.34</v>
-      </c>
-      <c r="C28" s="67">
-        <f>B28+B29</f>
-        <v>17122.580000000002</v>
-      </c>
-      <c r="D28" s="69">
-        <v>20031</v>
-      </c>
-      <c r="E28" s="71">
-        <v>46029</v>
-      </c>
-      <c r="F28" s="67">
-        <f>C28-D28</f>
-        <v>-2908.4199999999983</v>
-      </c>
-      <c r="G28" s="32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M28">
+        <v>2466.2399999999998</v>
+      </c>
+      <c r="O28">
+        <v>20035.419999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="4">
+        <v>10574.88</v>
+      </c>
+      <c r="C29" s="64">
+        <v>20400</v>
+      </c>
+      <c r="D29" s="76">
+        <v>20400</v>
+      </c>
+      <c r="E29" s="25">
+        <v>46051</v>
+      </c>
+      <c r="F29" s="19">
+        <f>C29-D29</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="23"/>
+      <c r="L29">
         <v>40</v>
       </c>
-      <c r="B29" s="4">
-        <v>9038.24</v>
-      </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="32"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M29">
+        <v>7862.97</v>
+      </c>
+      <c r="O29">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B30" s="4">
+        <v>9825.43</v>
+      </c>
+      <c r="C30" s="66"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="23"/>
+      <c r="L30">
+        <v>46</v>
+      </c>
+      <c r="M30">
+        <v>10157.86</v>
+      </c>
+      <c r="O30">
+        <f>O28+O29</f>
+        <v>19435.419999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1">
         <v>9877.56</v>
       </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="21"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="4">
-        <v>8311.7099999999991</v>
-      </c>
-      <c r="C31" s="67">
-        <f>B31+B32</f>
-        <v>16174.68</v>
-      </c>
-      <c r="D31" s="69">
-        <v>15028</v>
-      </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="67">
+      <c r="C31" s="64">
+        <f>B31+B32-600</f>
+        <v>19435.419999999998</v>
+      </c>
+      <c r="D31" s="76">
+        <v>19000</v>
+      </c>
+      <c r="E31" s="25">
+        <v>46092</v>
+      </c>
+      <c r="F31" s="19">
         <f>C31-D31</f>
-        <v>1146.6800000000003</v>
-      </c>
-      <c r="G31" s="75" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+        <v>435.41999999999825</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M31">
+        <f>SUM(M28:M30)</f>
+        <v>20487.07</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" s="4">
-        <v>7862.97</v>
-      </c>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="75"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="4">
-        <v>10574.88</v>
-      </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="21"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+        <v>10157.86</v>
+      </c>
+      <c r="C32" s="66"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="23"/>
+      <c r="L32" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="4">
-        <v>9825.43</v>
-      </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="21"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C36" s="13">
-        <f>SUM(C28:C35)</f>
-        <v>33297.26</v>
-      </c>
-      <c r="D36" s="13">
-        <f>SUM(D28:D35)</f>
-        <v>35059</v>
-      </c>
-      <c r="F36" s="13">
-        <f>SUM(F27:F35)</f>
-        <v>393.26000000000204</v>
+      <c r="M32">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="33" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C33" s="13">
+        <f>SUM(C2:C32)</f>
+        <v>283962.32999999996</v>
+      </c>
+      <c r="D33" s="63">
+        <f>SUM(D2:D32)</f>
+        <v>283201.58</v>
+      </c>
+      <c r="F33" s="13">
+        <f>SUM(F2:F32)</f>
+        <v>760.75000000000728</v>
+      </c>
+      <c r="M33">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="34" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="D34" s="77"/>
+      <c r="M34" t="e">
+        <f>#REF!-M33</f>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="79">
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="E31:E32"/>
     <mergeCell ref="C31:C32"/>
     <mergeCell ref="D31:D32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="C19:C22"/>
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:F22"/>
@@ -1634,22 +1660,43 @@
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="E27:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
